--- a/emergency_report_forms/007_theme_park_food_poisoning_incident_report--emergency_report_forms.xlsx
+++ b/emergency_report_forms/007_theme_park_food_poisoning_incident_report--emergency_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -890,12 +890,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>submitted_by_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Submitted By</t>
+          <t>Submitted By 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>submitted_by_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Submitted By</t>
+          <t>Submitted By 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>submitted_by_4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Submitted By</t>
+          <t>Submitted By 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>submitted_by_5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Submitted By</t>
+          <t>Submitted By 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>submitted_on</t>
+          <t>submitted_on_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Submitted On</t>
+          <t>Submitted On 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1608,7 +1608,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1625,7 +1625,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1642,7 +1642,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1710,7 +1710,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_3_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1727,7 +1727,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_3_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1744,7 +1744,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_3_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_4_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1778,7 +1778,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_4_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_4_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1812,7 +1812,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_5_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1829,7 +1829,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_5_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>submitted_by_5_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
